--- a/sheets/대금율보/검수/거문고.xlsx
+++ b/sheets/대금율보/검수/거문고.xlsx
@@ -3860,7 +3860,7 @@
       </c>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 –潢</t>
         </is>
       </c>
@@ -3900,7 +3900,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 –潢</t>
         </is>
       </c>
@@ -3957,7 +3957,7 @@
       <c r="K4" s="23"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢林‹
+          <t xml:space="preserve">潢林
 –潢</t>
         </is>
       </c>
@@ -3977,8 +3977,7 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
@@ -4135,7 +4134,7 @@
       <c r="K7" s="22"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃‹
+          <t xml:space="preserve">黃
 –夾</t>
         </is>
       </c>
@@ -4169,7 +4168,7 @@
       <c r="K8" s="23"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林夾‹
+          <t xml:space="preserve">林夾
 –林</t>
         </is>
       </c>
@@ -4236,8 +4235,7 @@
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">夾太
-黃
-‹</t>
+黃</t>
         </is>
       </c>
       <c r="M10" s="24"/>
@@ -4258,8 +4256,7 @@
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋淋
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -4354,7 +4351,7 @@
       </c>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–淋‹
+          <t xml:space="preserve">–淋
 淋</t>
         </is>
       </c>
@@ -4457,7 +4454,7 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞浹‹
+          <t xml:space="preserve">㳞浹
 浹汰</t>
         </is>
       </c>
@@ -4577,14 +4574,14 @@
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳潢‹
+          <t xml:space="preserve">湳潢
 –湳淋</t>
         </is>
       </c>
@@ -4611,7 +4608,7 @@
       <c r="C17" s="23"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢‹
+          <t xml:space="preserve">潢潢
 –汰</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/거문고.xlsx
+++ b/sheets/대금율보/검수/거문고.xlsx
@@ -3809,24 +3809,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="61.54" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="68.7" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="68.7" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="68.7" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="M5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="68.7" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="M6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="68.7" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="68.7" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="M8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="68.7" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="M9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="68.7" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="M10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="68.7" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="68.7" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="M12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="68.7" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="68.7" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="M14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="68.7" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="68.7" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="M16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="68.7" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="M17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="68.7" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -4704,6 +4704,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="65"/>
 </worksheet>
 </file>